--- a/ig/ch-epl/StructureDefinition-regulatedAuthorization-limitation.xlsx
+++ b/ig/ch-epl/StructureDefinition-regulatedAuthorization-limitation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="196">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>CH - EPL Regulated Authorization Limitation</t>
+    <t>CH EPL - Regulated Authorization Limitation</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-20</t>
+    <t>2026-02-25</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -533,6 +533,73 @@
 </t>
   </si>
   <si>
+    <t>Extension.extension:priceModelSpecification</t>
+  </si>
+  <si>
+    <t>priceModelSpecification</t>
+  </si>
+  <si>
+    <t>Specification of the Price Model</t>
+  </si>
+  <si>
+    <t>Extension.extension:priceModelSpecification.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:priceModelSpecification.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:priceModelSpecification.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:priceModelSpecification.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension:priceModel</t>
+  </si>
+  <si>
+    <t>priceModel</t>
+  </si>
+  <si>
+    <t>Indicator for a Price Model</t>
+  </si>
+  <si>
+    <t>Extension.extension:priceModel.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:priceModel.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:priceModel.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:priceModel.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Extension.extension:relatedIndication</t>
+  </si>
+  <si>
+    <t>relatedIndication</t>
+  </si>
+  <si>
+    <t>Reference to the indication related to this limitation</t>
+  </si>
+  <si>
+    <t>Extension.extension:relatedIndication.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:relatedIndication.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:relatedIndication.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:relatedIndication.value[x]</t>
+  </si>
+  <si>
     <t>Extension.extension:productPrice</t>
   </si>
   <si>
@@ -543,7 +610,7 @@
 </t>
   </si>
   <si>
-    <t>CH - EPL Product Price</t>
+    <t>CH EPL - Product Price</t>
   </si>
   <si>
     <t>A set of information about the price of a drug</t>
@@ -872,7 +939,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK42"/>
+  <dimension ref="A1:AK57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.3828125" customWidth="true" bestFit="true"/>
@@ -4986,7 +5053,7 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>78</v>
@@ -4998,13 +5065,13 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5075,10 +5142,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>112</v>
+        <v>171</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5086,7 +5153,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>80</v>
@@ -5101,24 +5168,22 @@
         <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>78</v>
@@ -5160,30 +5225,30 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>113</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5206,13 +5271,13 @@
         <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>173</v>
+        <v>93</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>117</v>
+        <v>32</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5251,33 +5316,1592 @@
         <v>78</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AF42" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AG42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI42" t="s" s="2">
+      <c r="AG44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI44" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="AJ42" t="s" s="2">
+      <c r="AJ44" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="AK42" t="s" s="2">
+      <c r="AK44" t="s" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="D45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="D50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="D55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AK57" t="s" s="2">
         <v>113</v>
       </c>
     </row>
